--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.51464</v>
+        <v>16.74625</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68743</v>
+        <v>16.48581</v>
       </c>
       <c r="E2" t="n">
-        <v>16.79365</v>
+        <v>16.66966</v>
       </c>
       <c r="F2" t="n">
-        <v>42.14348</v>
+        <v>42.66628</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04989</v>
+        <v>0.05134</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80214</v>
+        <v>1.86501</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.90419</v>
+        <v>16.94172</v>
       </c>
       <c r="D3" t="n">
-        <v>16.59137</v>
+        <v>16.61402</v>
       </c>
       <c r="E3" t="n">
-        <v>16.83455</v>
+        <v>16.63831</v>
       </c>
       <c r="F3" t="n">
-        <v>42.12059</v>
+        <v>42.28995</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05114</v>
+        <v>0.05056</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80266</v>
+        <v>1.81891</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65586</v>
+        <v>16.67162</v>
       </c>
       <c r="D4" t="n">
-        <v>16.86049</v>
+        <v>16.3756</v>
       </c>
       <c r="E4" t="n">
-        <v>17.20389</v>
+        <v>16.56654</v>
       </c>
       <c r="F4" t="n">
-        <v>42.2262</v>
+        <v>42.93978</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05101</v>
+        <v>0.05094</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83647</v>
+        <v>1.83371</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.88497</v>
+        <v>16.63809</v>
       </c>
       <c r="D6" t="n">
-        <v>15.90378</v>
+        <v>15.90397</v>
       </c>
       <c r="E6" t="n">
-        <v>16.60739</v>
+        <v>16.18093</v>
       </c>
       <c r="F6" t="n">
-        <v>21.53232</v>
+        <v>22.04344</v>
       </c>
       <c r="G6" t="n">
-        <v>33.61142</v>
+        <v>33.99568</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.78165</v>
+        <v>16.74203</v>
       </c>
       <c r="D7" t="n">
-        <v>16.06024</v>
+        <v>16.21612</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76983</v>
+        <v>16.48783</v>
       </c>
       <c r="F7" t="n">
-        <v>22.01259</v>
+        <v>21.81322</v>
       </c>
       <c r="G7" t="n">
-        <v>34.2182</v>
+        <v>33.68983</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.26546</v>
+        <v>16.59715</v>
       </c>
       <c r="D8" t="n">
-        <v>16.01101</v>
+        <v>15.97427</v>
       </c>
       <c r="E8" t="n">
-        <v>16.23837</v>
+        <v>16.5373</v>
       </c>
       <c r="F8" t="n">
-        <v>22.1673</v>
+        <v>22.06678</v>
       </c>
       <c r="G8" t="n">
-        <v>33.79518</v>
+        <v>34.3421</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6151</v>
+        <v>0.6119</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12631</v>
+        <v>1.12034</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.59904</v>
+        <v>0.61129</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13504</v>
+        <v>1.11268</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59804</v>
+        <v>0.6085</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12215</v>
+        <v>1.15124</v>
       </c>
     </row>
   </sheetData>
